--- a/en/downloads/data-excel/5.5.1.xlsx
+++ b/en/downloads/data-excel/5.5.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="10935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +321,12 @@
     </font>
     <font>
       <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -394,7 +400,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -459,6 +465,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -757,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="36" customWidth="1"/>
@@ -765,7 +777,7 @@
     <col min="5" max="20" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="31.5" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>3</v>
       </c>
@@ -786,7 +798,7 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1">
+    <row r="2" spans="1:21" s="1" customFormat="1">
       <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
@@ -807,7 +819,7 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -822,8 +834,9 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="2"/>
+      <c r="U3" s="21"/>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1">
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -884,8 +897,11 @@
       <c r="T4" s="26" t="s">
         <v>13</v>
       </c>
+      <c r="U4" s="27">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="16" customFormat="1" ht="27" customHeight="1">
+    <row r="5" spans="1:21" s="16" customFormat="1" ht="27" customHeight="1">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -946,8 +962,11 @@
       <c r="T5" s="15">
         <v>22.2</v>
       </c>
+      <c r="U5" s="28">
+        <v>22.2</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" s="19" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:21" s="19" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="s">
         <v>14</v>
       </c>
@@ -1008,8 +1027,11 @@
       <c r="T6" s="22">
         <v>37.9</v>
       </c>
+      <c r="U6" s="22">
+        <v>39.799999999999997</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" s="21" customFormat="1">
+    <row r="7" spans="1:21" s="21" customFormat="1">
       <c r="A7" s="20" t="s">
         <v>17</v>
       </c>
